--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129490838</v>
       </c>
       <c r="B2" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,6 +781,107 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129517040</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>604785</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6978990</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129490838</v>
       </c>
       <c r="B2" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129490838</v>
       </c>
       <c r="B2" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129490838</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129517040</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129490838</v>
       </c>
       <c r="B2" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129517040</v>
       </c>
       <c r="B3" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129490838</v>
       </c>
       <c r="B2" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129517040</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129490838</v>
       </c>
       <c r="B2" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,6 +883,133 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129805841</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>604808</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6978964</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129490838</v>
       </c>
       <c r="B2" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129490838</v>
       </c>
       <c r="B2" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1010,6 +1010,111 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129917799</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>604708</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6979030</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>129805841</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>129917799</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>129805841</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>129917799</v>
       </c>
       <c r="B5" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -1015,7 +1015,7 @@
         <v>129917799</v>
       </c>
       <c r="B5" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -1015,7 +1015,7 @@
         <v>129917799</v>
       </c>
       <c r="B5" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -1015,7 +1015,7 @@
         <v>129917799</v>
       </c>
       <c r="B5" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -1015,7 +1015,7 @@
         <v>129917799</v>
       </c>
       <c r="B5" t="n">
-        <v>80285</v>
+        <v>80200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1115,6 +1115,111 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134420318</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>604743</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6978990</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129490838</v>
       </c>
       <c r="B2" t="n">
-        <v>92919</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129517040</v>
+        <v>129917799</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,27 +795,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604785</v>
+        <v>604708</v>
       </c>
       <c r="R3" t="n">
-        <v>6978990</v>
+        <v>6979030</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -853,12 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,6 +870,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,7 +892,7 @@
         <v>129805841</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129917799</v>
+        <v>129917445</v>
       </c>
       <c r="B5" t="n">
-        <v>80285</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1045,19 +1049,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604708</v>
+        <v>604740</v>
       </c>
       <c r="R5" t="n">
-        <v>6979030</v>
+        <v>6978947</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1087,18 +1104,32 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sannolikt samma individ som i obsen strax innan.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1220,6 +1251,107 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129517040</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>604785</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6978990</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26338-2025 artfynd.xlsx
+++ b/artfynd/A 26338-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129490838</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129917799</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805841</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129917445</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1250,6 +1275,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134420318</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1351,8 +1381,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129517040</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>